--- a/output/pdf_financials_xlsx/STCU.xlsx
+++ b/output/pdf_financials_xlsx/STCU.xlsx
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>3.4313</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.657102</v>
       </c>
     </row>
     <row r="93">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.555312</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.181108</v>
       </c>
     </row>
     <row r="104">
@@ -2253,13 +2253,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.663087</v>
+        <v>1.218399</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.583178</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>1.191766</v>
+        <v>1.010658</v>
       </c>
     </row>
     <row r="107">
@@ -2906,7 +2906,11 @@
           <t>Prepaids and deposits (Note 5)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -3261,7 +3265,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3660,7 +3668,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>0.555312</v>
       </c>

--- a/output/pdf_financials_xlsx/STCU.xlsx
+++ b/output/pdf_financials_xlsx/STCU.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.00072</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001562</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.027819</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.449707</v>
+        <v>-2.450427</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.438266</v>
+        <v>-5.439828</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-5.242742</v>
+        <v>-5.270561</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.392152</v>
+        <v>-2.392872</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.433604</v>
+        <v>-5.435166</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.239013</v>
+        <v>-5.266832</v>
       </c>
     </row>
     <row r="30">
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.009735000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>6.061599</v>
       </c>
     </row>
     <row r="35">
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.009735000000000001</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>6.061599</v>
       </c>
     </row>
     <row r="37">
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.052855</v>
+        <v>0.04312</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>6.600784</v>
+        <v>0.539185</v>
       </c>
     </row>
     <row r="49">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">

--- a/output/pdf_financials_xlsx/STCU.xlsx
+++ b/output/pdf_financials_xlsx/STCU.xlsx
@@ -975,10 +975,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.034379</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.009735000000000001</v>
@@ -993,10 +991,8 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>
@@ -1011,10 +1007,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.034379</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.009735000000000001</v>
@@ -1029,10 +1023,8 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0</v>
@@ -1047,10 +1039,8 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>0</v>
@@ -1065,10 +1055,8 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -1083,10 +1071,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0</v>
@@ -1101,10 +1087,8 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0</v>
@@ -1119,10 +1103,8 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>0</v>
@@ -1137,10 +1119,8 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
@@ -1155,10 +1135,8 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -1173,10 +1151,8 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -1191,10 +1167,8 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0</v>
@@ -1209,10 +1183,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0</v>
@@ -1227,10 +1199,8 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.2659</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.04312</v>
@@ -1245,10 +1215,8 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0.300279</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>0.052855</v>
@@ -1263,10 +1231,8 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0</v>
@@ -1281,10 +1247,8 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>0</v>
@@ -1299,10 +1263,8 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>0</v>
@@ -1317,10 +1279,8 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0</v>
@@ -1335,10 +1295,8 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>0</v>
@@ -1375,10 +1333,8 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>0</v>
@@ -1393,10 +1349,8 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>0</v>
@@ -1411,10 +1365,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>10.636425</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>6.565296</v>
@@ -1429,10 +1381,8 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>0</v>
@@ -1447,10 +1397,8 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>0</v>
@@ -1465,10 +1413,8 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0.1095</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0.1095</v>
@@ -1483,10 +1429,8 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>10.745925</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>6.674796</v>
@@ -1501,10 +1445,8 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>11.046204</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>6.727651</v>
@@ -1519,10 +1461,8 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>0</v>
@@ -1537,10 +1477,8 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>0</v>
@@ -1555,10 +1493,8 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0</v>
@@ -1573,10 +1509,8 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0</v>
@@ -1591,10 +1525,8 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.637819</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.939813</v>
@@ -1609,10 +1541,8 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>0.390248</v>
@@ -1627,10 +1557,8 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
@@ -1645,10 +1573,8 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0.390248</v>
@@ -1663,10 +1589,8 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>0</v>
@@ -1681,10 +1605,8 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C73" s="3" t="n">
         <v>0</v>
@@ -1699,10 +1621,8 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>0</v>
@@ -1717,10 +1637,8 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0.119408</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0</v>
@@ -1735,10 +1653,8 @@
           <t xml:space="preserve">  Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>0.757227</v>
       </c>
       <c r="C76" s="3" t="n">
         <v>1.330061</v>
@@ -1753,10 +1669,8 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>0</v>
@@ -1771,10 +1685,8 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0</v>
@@ -1789,10 +1701,8 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0</v>
@@ -1827,10 +1737,8 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>0</v>
@@ -1845,10 +1753,8 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>0</v>
@@ -1863,10 +1769,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>0</v>
@@ -1881,10 +1785,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>0</v>
@@ -1899,10 +1801,8 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>0</v>
@@ -1917,10 +1817,8 @@
           <t xml:space="preserve">  Total Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C86" s="3" t="n">
         <v>0</v>
@@ -1935,10 +1833,8 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>0.757227</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>1.330061</v>
@@ -1953,10 +1849,8 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>18.074487</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>18.621366</v>
@@ -1971,10 +1865,8 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0</v>
@@ -1989,10 +1881,8 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>-11.21681</v>
       </c>
       <c r="C90" s="3" t="n">
         <v>-16.655076</v>
@@ -2007,10 +1897,8 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0</v>
@@ -2025,10 +1913,8 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>3.4313</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>3.4313</v>
@@ -2043,10 +1929,8 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>0</v>
@@ -2061,10 +1945,8 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>10.288977</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>5.39759</v>
@@ -2079,10 +1961,8 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>0</v>
@@ -2097,10 +1977,8 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>10.288977</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>5.39759</v>
@@ -2115,10 +1993,8 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.9314491204399267</v>
       </c>
       <c r="C97" s="3" t="n">
         <v>0.80229934638405</v>
@@ -2743,7 +2619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2810,10 +2686,8 @@
           <t>CashAndCashEquivalents</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E2" s="5" t="n">
+        <v>0.034379</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0.009735000000000001</v>
@@ -2843,10 +2717,8 @@
           <t>TaxesReceivable</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E3" s="5" t="n">
+        <v>0.23445</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.04042</v>
@@ -2944,10 +2816,8 @@
           <t>CurrentAssets</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="5" t="n">
+        <v>0.300279</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.052855</v>
@@ -2973,10 +2843,8 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="5" t="n">
+        <v>0.1095</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.1095</v>
@@ -3072,10 +2940,8 @@
           <t>TotalAssets</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="5" t="n">
+        <v>11.046204</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>6.727651</v>
@@ -3204,10 +3070,8 @@
           <t>CurrentLiabilities</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="5" t="n">
+        <v>0.757227</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>1.330061</v>
@@ -3303,10 +3167,8 @@
           <t>RetainedEarnings</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="5" t="n">
+        <v>-11.21681</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>-16.655076</v>
@@ -3384,200 +3246,220 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>Restricted cash (Note 4)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>RestrictedCash</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-2.449707</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>-5.438266</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-5.242742</v>
+        <v>0.02875</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Prepaid and deposits (Note 5)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>PrepaidAssets</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.057555</v>
+        <v>0.0027</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.004662</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>0.003729</v>
+        <v>0.0027</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Flow-through premium recovery</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Property and equipment (Note 8)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.023309</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-0.060408</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>-0.03385</v>
+        <v>0.018647</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Interest expense</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Exploration and evaluation assets (Note 9)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E23" s="5" t="n">
-        <v>0.045039</v>
+        <v>10.613116</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.027127</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>0.019752</v>
+        <v>6.546649</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Loss disposition of asset upon spin-out</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>1.083842</v>
+          <t>Accounts payable and accrued liabilities (Note 10 &amp; 13) $</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.637819</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.939813</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Property impairment</t>
+          <t>Flow-through premium liability (Note 17)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>5.018474</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0.018</v>
+      <c r="E25" s="5" t="n">
+        <v>0.119408</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable</t>
+          <t>Loans payable (Note 11)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3586,134 +3468,144 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.023348</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>-0.09014800000000001</v>
+        <v>0.390248</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
+          <t>Share capital (Note 12)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.125004</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>1.09</v>
+        <v>18.074487</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>18.621366</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Goods and services taxes receivable</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Reserves</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
-        <v>-0.072658</v>
+        <v>3.4313</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.19403</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>-0.282959</v>
+        <v>3.4313</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prepaid and deposits</t>
+          <t>Total shareholder’s equity</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.555312</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>-0.181108</v>
+        <v>10.288977</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>5.39759</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Total liabilities and shareholder’s equity $</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.322903</v>
+        <v>11.046204</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.355303</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>-0.345869</v>
+        <v>6.727651</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -3724,25 +3616,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Net cash (used in) provided by operations</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>-2.449707</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.077574</v>
+        <v>-5.438266</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-3.961353</v>
+        <v>-5.242742</v>
       </c>
     </row>
     <row r="32">
@@ -3753,27 +3647,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-2.11458</v>
+        <v>0.057555</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.540968</v>
+        <v>0.004662</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-2.693473</v>
+        <v>0.003729</v>
       </c>
     </row>
     <row r="33">
@@ -3784,12 +3678,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Investment</t>
+          <t>Flow-through premium recovery</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -3798,13 +3692,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F33" s="5" t="n">
+        <v>-0.060408</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.049998</v>
+        <v>-0.03385</v>
       </c>
     </row>
     <row r="34">
@@ -3815,27 +3707,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Refund of deposit</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E34" s="5" t="n">
+        <v>0.045039</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.02875</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.027127</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.019752</v>
       </c>
     </row>
     <row r="35">
@@ -3846,29 +3734,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Loss disposition of asset upon spin-out</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F35" s="5" t="n">
-        <v>-0.512218</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-2.743471</v>
+        <v>1.083842</v>
       </c>
     </row>
     <row r="36">
@@ -3879,12 +3765,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Proceeds from loans payable</t>
+          <t>Property impairment</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3894,10 +3780,10 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.41</v>
+        <v>5.018474</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.41</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="37">
@@ -3908,17 +3794,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of shares</t>
+          <t>Gain on settlement of accounts payable</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3926,13 +3812,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F37" s="5" t="n">
+        <v>-0.023348</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>12.748451</v>
+        <v>-0.09014800000000001</v>
       </c>
     </row>
     <row r="38">
@@ -3943,17 +3827,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Proceeds from exercise of warrants</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
-        <v>0.721</v>
+        <v>0.125004</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3961,7 +3849,7 @@
         </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.565349</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="39">
@@ -3972,31 +3860,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Goods and services taxes receivable</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" s="5" t="n">
+        <v>-0.072658</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.19403</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.147112</v>
+        <v>-0.282959</v>
       </c>
     </row>
     <row r="40">
@@ -4007,27 +3887,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Prepaid and deposits</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.7111</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0.41</v>
+        <v>0.555312</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G40" s="5" t="n">
-        <v>12.756688</v>
+        <v>-0.181108</v>
       </c>
     </row>
     <row r="41">
@@ -4038,29 +3920,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net increase (decrease) in cash</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.322903</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-0.024644</v>
+        <v>0.355303</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>6.051864</v>
+        <v>-0.345869</v>
       </c>
     </row>
     <row r="42">
@@ -4071,27 +3951,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>3.156069</v>
+          <t>Net cash (used in) provided by operations</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.034379</v>
+        <v>0.077574</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.009735000000000001</v>
+        <v>-3.961353</v>
       </c>
     </row>
     <row r="43">
@@ -4102,27 +3980,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
+          <t>Exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EndCashPosition</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.034379</v>
+        <v>-2.11458</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.009735000000000001</v>
+        <v>-0.540968</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>6.061599</v>
+        <v>-2.693473</v>
       </c>
     </row>
     <row r="44">
@@ -4133,12 +4011,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shares issued for property payment $</t>
+          <t>Investment</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4147,11 +4025,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>0.5</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.286</v>
+        <v>-0.049998</v>
       </c>
     </row>
     <row r="45">
@@ -4162,26 +4042,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shares issued for bonus payment on issuance of debt $</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>IssuanceOfDebt</t>
-        </is>
-      </c>
+          <t>Refund of deposit</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.046879</v>
+        <v>0.02875</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4197,27 +4073,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Exploration and evaluation costs included in accounts payable and accrued liabilities $</t>
+          <t>Net cash used in investing activities</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>0.340184</v>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.251223</v>
+        <v>-0.512218</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>1.627783</v>
+        <v>-2.743471</v>
       </c>
     </row>
     <row r="47">
@@ -4228,25 +4106,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Flow-through premium recovery, net of provision</t>
+          <t>Proceeds from loans payable</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" s="5" t="n">
-        <v>-0.178062</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>-0.060408</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.41</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="48">
@@ -4257,27 +4135,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gain on extinguishment of lease</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" s="5" t="n">
-        <v>-0.126478</v>
+          <t>Proceeds from issuance of shares</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G48" s="5" t="n">
+        <v>12.748451</v>
       </c>
     </row>
     <row r="49">
@@ -4288,25 +4170,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Net cash provided by (used in) operations</t>
+          <t>Proceeds from exercise of warrants</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>-1.721092</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>0.077574</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.721</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.565349</v>
       </c>
     </row>
     <row r="50">
@@ -4317,27 +4199,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Refund of deposit (Note 4)</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F50" s="5" t="n">
-        <v>0.02875</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>-0.147112</v>
       </c>
     </row>
     <row r="51">
@@ -4348,31 +4234,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Purchase of property and equipment</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PurchaseOfPPE</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>-0.002751</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.7111</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>12.756688</v>
       </c>
     </row>
     <row r="52">
@@ -4383,27 +4265,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lease obligations</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" s="5" t="n">
-        <v>-0.09243</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net increase (decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>-0.024644</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>6.051864</v>
       </c>
     </row>
     <row r="53">
@@ -4414,27 +4298,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cash acquired on acquisition of CAVU</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E53" s="5" t="n">
-        <v>0.098063</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.156069</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.034379</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.009735000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4445,29 +4329,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Net cash (used in) investing activities</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>-2.111698</v>
+        <v>0.034379</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-0.512218</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.009735000000000001</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>6.061599</v>
       </c>
     </row>
     <row r="55">
@@ -4483,26 +4365,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>-0.009900000000000001</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shares issued for property payment $</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.286</v>
       </c>
     </row>
     <row r="56">
@@ -4518,19 +4394,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Net decrease in cash</t>
+          <t>Shares issued for bonus payment on issuance of debt $</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>-3.12169</v>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F56" s="5" t="n">
-        <v>-0.024644</v>
+        <v>0.046879</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4551,22 +4429,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Shares issued for acquisition of CAVU Energy Metals Corp. $</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Exploration and evaluation costs included in accounts payable and accrued liabilities $</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
-        <v>5.351853</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.340184</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>0.251223</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>1.627783</v>
       </c>
     </row>
     <row r="58">
@@ -4577,20 +4455,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>(“IFRIC”).</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>(“IFRIC”). total</t>
+          <t>Flow-through premium recovery, net of provision</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>0.002025</v>
+        <v>-0.178062</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>2.8e-05</v>
+        <v>-0.060408</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -4601,344 +4479,350 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Consulting fees (Notes 12 &amp; 15) $</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>0.200871</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>0.261666</v>
+          <t>Gain on extinguishment of lease</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" s="5" t="n">
+        <v>-0.126478</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Marketing and investor relations (Note 15)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash provided by (used in) operations</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>-1.721092</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.09363200000000001</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>2.190068</v>
+        <v>0.077574</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Office and administration (Notes 12 &amp; 15)</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Refund of deposit (Note 4)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.084422</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0.092309</v>
+        <v>0.02875</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Purchase of property and equipment</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>PurchaseOfPPE</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0.292843</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>0.07795100000000001</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.517748</v>
+        <v>-0.002751</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Regulatory and filing</t>
+          <t>Lease obligations</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
-        <v>0.059503</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0.043572</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.092864</v>
+        <v>-0.09243</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 11)</t>
+          <t>Cash acquired on acquisition of CAVU</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="5" t="n">
+        <v>0.098063</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G64" s="5" t="n">
-        <v>1.09</v>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Travel expenses</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>0.044333</v>
+          <t>Net cash (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>-2.111698</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>-0.512218</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Depreciation (Note 7)</t>
+          <t>Share issue costs</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0.004662</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>0.003729</v>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Net loss before other items</t>
+          <t>Net decrease in cash</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>-2.735467</v>
+        <v>-3.12169</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>-0.5051099999999999</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>-4.292717</v>
+        <v>-0.024644</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Flow-through premium recovery (Note 17)</t>
+          <t>Shares issued for acquisition of CAVU Energy Metals Corp. $</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>0.060408</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>0.03385</v>
+      <c r="E68" s="5" t="n">
+        <v>5.351853</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>(“IFRIC”).</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>(“IFRIC”). total</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" s="5" t="n">
-        <v>0.00072</v>
+        <v>0.002025</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.001562</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>0.027819</v>
+        <v>2.8e-05</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -4949,27 +4833,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Loss disposition of asset upon spin-out (Note 4)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Consulting fees (Notes 12 &amp; 15) $</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F70" s="5" t="n">
+        <v>0.200871</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>-1.083842</v>
+        <v>0.261666</v>
       </c>
     </row>
     <row r="71">
@@ -4980,25 +4866,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Property impairment (Note 8)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Marketing and investor relations (Note 15)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>-5.018474</v>
+        <v>0.09363200000000001</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.018</v>
+        <v>2.190068</v>
       </c>
     </row>
     <row r="72">
@@ -5009,25 +4899,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Office and administration (Notes 12 &amp; 15)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.023348</v>
+        <v>0.084422</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.09014800000000001</v>
+        <v>0.092309</v>
       </c>
     </row>
     <row r="73">
@@ -5038,27 +4932,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>-2.449707</v>
+        <v>0.292843</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-5.438266</v>
+        <v>0.07795100000000001</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>-5.242742</v>
+        <v>0.517748</v>
       </c>
     </row>
     <row r="74">
@@ -5069,27 +4963,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Weighted average numbers of shares outstanding</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Regulatory and filing</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" s="5" t="n">
-        <v>8.036797999999999</v>
+        <v>0.059503</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>9.590271</v>
+        <v>0.043572</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>26.679874</v>
+        <v>0.092864</v>
       </c>
     </row>
     <row r="75">
@@ -5100,27 +4990,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>-3e-07</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>-5.699999999999999e-07</v>
+          <t>Share-based compensation (Note 11)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-2e-07</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="76">
@@ -5131,12 +5021,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t># of shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Balance, September 30, 2023 8,923,491 $ 18,074,487 $ 3,431,300 $</t>
+          <t>Travel expenses</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -5145,11 +5035,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F76" s="5" t="n">
-        <v>10.288977</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>-11.21681</v>
+        <v>0.044333</v>
       </c>
     </row>
     <row r="77">
@@ -5160,27 +5052,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t># of shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Shares issued for mineral properties (Notes 8 &amp; 11) 567,537 500,000 -</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>Depreciation (Note 7)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.004662</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.003729</v>
       </c>
     </row>
     <row r="78">
@@ -5191,27 +5085,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t># of shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Shares issued on issuance of debt (Notes 10 &amp; 11) 290,000 46,879 -</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss before other items</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>-2.735467</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.046879</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.5051099999999999</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>-4.292717</v>
       </c>
     </row>
     <row r="79">
@@ -5222,29 +5116,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t># of shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Flow-through premium recovery (Note 17)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-5.438266</v>
+        <v>0.060408</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-5.438266</v>
+        <v>0.03385</v>
       </c>
     </row>
     <row r="80">
@@ -5255,25 +5145,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t># of shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Balance, September 30, 2024 9,781,028 $ 18,621,366 $ 3,431,300 $</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>0.00072</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>5.39759</v>
+        <v>0.001562</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>-16.655076</v>
+        <v>0.027819</v>
       </c>
     </row>
     <row r="81">
@@ -5284,12 +5176,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t># of shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Flow-through shares issued for cash (Note 11) 6,177,108 5,894,284 -</t>
+          <t>Loss disposition of asset upon spin-out (Note 4)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -5298,13 +5190,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F81" s="5" t="n">
-        <v>5.894284</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>-1.083842</v>
       </c>
     </row>
     <row r="82">
@@ -5315,12 +5207,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t># of shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Shares issued for cash (Note 11) 27,504,998 6,747,500 -</t>
+          <t>Property impairment (Note 8)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -5330,12 +5222,10 @@
         </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>6.7475</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.018474</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>-0.018</v>
       </c>
     </row>
     <row r="83">
@@ -5346,12 +5236,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t># of shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Shares issued for property (Notes 8 &amp; 11) 200,000 286,000 -</t>
+          <t>Gain on settlement of accounts payable</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -5361,12 +5251,10 @@
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.023348</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.09014800000000001</v>
       </c>
     </row>
     <row r="84">
@@ -5377,27 +5265,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t># of shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Warrant exercises (Note 11) 3,327,066 597,151 -</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>-2.449707</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.597151</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.438266</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>-5.242742</v>
       </c>
     </row>
     <row r="85">
@@ -5408,27 +5296,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t># of shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Warrant proceeds paid to Alpha (Note 11) - (31,802) -</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average numbers of shares outstanding</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>8.036797999999999</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>-0.031802</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.590271</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>26.679874</v>
       </c>
     </row>
     <row r="86">
@@ -5439,27 +5327,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t># of shares</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Disposition of asset upon spin-out (Note 4) - (864,960) -</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>-3e-07</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>-0.86496</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.699999999999999e-07</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>-2e-07</v>
       </c>
     </row>
     <row r="87">
@@ -5475,7 +5363,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Share issuance costs (Note 11) - (282,914) 135,802</t>
+          <t>Balance, September 30, 2023 8,923,491 $ 18,074,487 $ 3,431,300 $</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -5485,12 +5373,10 @@
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>-0.147112</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.288977</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>-11.21681</v>
       </c>
     </row>
     <row r="88">
@@ -5506,7 +5392,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 11) - - 1,090,000</t>
+          <t>Shares issued for mineral properties (Notes 8 &amp; 11) 567,537 500,000 -</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -5516,7 +5402,7 @@
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>1.09</v>
+        <v>0.5</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5537,7 +5423,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Balance, September 30, 2025 46,990,200 $ 30,966,625 $ 4,657,102 $</t>
+          <t>Shares issued on issuance of debt (Notes 10 &amp; 11) 290,000 46,879 -</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -5547,10 +5433,12 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>13.725909</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>-21.897818</v>
+        <v>0.046879</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -5561,29 +5449,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t># of shares</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 13 &amp; 16) $</t>
+          <t>Net loss for the year - - -</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="n">
-        <v>0.402505</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.200871</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-5.438266</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>-5.438266</v>
       </c>
     </row>
     <row r="91">
@@ -5594,29 +5482,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t># of shares</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Marketing and investor relations (Note 16)</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="n">
-        <v>1.63187</v>
+          <t>Balance, September 30, 2024 9,781,028 $ 18,621,366 $ 3,431,300 $</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.09363200000000001</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.39759</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-16.655076</v>
       </c>
     </row>
     <row r="92">
@@ -5627,24 +5511,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t># of shares</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Office and administration (Note 11 &amp; 13)</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="n">
-        <v>0.166187</v>
+          <t>Flow-through shares issued for cash (Note 11) 6,177,108 5,894,284 -</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.084422</v>
+        <v>5.894284</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5660,22 +5542,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t># of shares</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 12)</t>
+          <t>Shares issued for cash (Note 11) 27,504,998 6,747,500 -</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" s="5" t="n">
-        <v>0.125004</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>6.7475</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5691,24 +5573,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t># of shares</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Depreciation (Note 7 &amp; 8)</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>0.057555</v>
+          <t>Shares issued for property (Notes 8 &amp; 11) 200,000 286,000 -</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.004662</v>
+        <v>0.286</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5724,20 +5604,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t># of shares</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Flow-through premium recovery, net of provision</t>
+          <t>Warrant exercises (Note 11) 3,327,066 597,151 -</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" s="5" t="n">
-        <v>0.178062</v>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.060408</v>
+        <v>0.597151</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5753,12 +5635,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t># of shares</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Property impairment (Note 9)</t>
+          <t>Warrant proceeds paid to Alpha (Note 11) - (31,802) -</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -5768,7 +5650,7 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-5.018474</v>
+        <v>-0.031802</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -5784,22 +5666,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t># of shares</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Write-off of receivables</t>
+          <t>Disposition of asset upon spin-out (Note 4) - (864,960) -</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" s="5" t="n">
-        <v>-0.0195</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>-0.86496</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5815,22 +5697,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t># of shares</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Gain on extinguishment of lease (Note 7)</t>
+          <t>Share issuance costs (Note 11) - (282,914) 135,802</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" s="5" t="n">
-        <v>0.126478</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>-0.147112</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5846,20 +5728,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t># of shares*</t>
+          <t># of shares</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Balance, September 30, 2022 5,774,989 $ 12,002,394 $ 1,942,635 $</t>
+          <t>Share-based compensation (Note 11) - - 1,090,000</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
-      <c r="E99" s="5" t="n">
-        <v>5.177926</v>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>-8.767103000000001</v>
+        <v>1.09</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5875,27 +5759,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t># of shares*</t>
+          <t># of shares</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Acquisition of CAVU 2,548,502 5,351,853 1,365,551</t>
+          <t>Balance, September 30, 2025 46,990,200 $ 30,966,625 $ 4,657,102 $</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" s="5" t="n">
-        <v>6.717404</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>13.725909</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>-21.897818</v>
       </c>
     </row>
     <row r="101">
@@ -5906,22 +5788,24 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t># of shares*</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Share issue costs - (9,900) -</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Consulting fees (Note 13 &amp; 16) $</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
-        <v>-0.009900000000000001</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.402505</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.200871</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5937,22 +5821,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t># of shares*</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Exercise of warrants (Note 12) 595,000 722,890 (1,890)</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
+          <t>Marketing and investor relations (Note 16)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E102" s="5" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.63187</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>0.09363200000000001</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5968,22 +5854,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t># of shares*</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Shares issued for mineral properties (Note 9) 5,000 7,250 -</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>Office and administration (Note 11 &amp; 13)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E103" s="5" t="n">
-        <v>0.00725</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.166187</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.084422</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5999,12 +5887,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t># of shares*</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 12) - - 125,004</t>
+          <t>Share-based compensation (Note 12)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -6030,24 +5918,24 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t># of shares*</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Net loss for the year - - -</t>
+          <t>Depreciation (Note 7 &amp; 8)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>-2.449707</v>
+        <v>0.057555</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>-2.449707</v>
+        <v>0.004662</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -6063,20 +5951,20 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t># of shares*</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Balance, September 30, 2023 8,923,491 $ 18,074,487 $ 3,431,300 $</t>
+          <t>Flow-through premium recovery, net of provision</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" s="5" t="n">
-        <v>10.288977</v>
+        <v>0.178062</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>-11.21681</v>
+        <v>0.060408</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6092,22 +5980,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t># of shares*</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Shares issued for mineral properties (Note 9) 567,537 500,000 -</t>
+          <t>Property impairment (Note 9)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>-5.018474</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -6123,17 +6011,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t># of shares*</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Shares issued on issuance of debt (Note 11) 290,000 46,879 -</t>
+          <t>Write-off of receivables</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" s="5" t="n">
-        <v>0.046879</v>
+        <v>-0.0195</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -6154,22 +6042,361 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t># of shares*</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Balance, September 30, 2024 9,781,028 $ 18,621,366 $ 3,431,300 $</t>
+          <t>Gain on extinguishment of lease (Note 7)</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" s="5" t="n">
+        <v>0.126478</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t># of shares*</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Balance, September 30, 2022 5,774,989 $ 12,002,394 $ 1,942,635 $</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" s="5" t="n">
+        <v>5.177926</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>-8.767103000000001</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t># of shares*</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Acquisition of CAVU 2,548,502 5,351,853 1,365,551</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" s="5" t="n">
+        <v>6.717404</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t># of shares*</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Share issue costs - (9,900) -</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" s="5" t="n">
+        <v>-0.009900000000000001</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t># of shares*</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Exercise of warrants (Note 12) 595,000 722,890 (1,890)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" s="5" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t># of shares*</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Shares issued for mineral properties (Note 9) 5,000 7,250 -</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" s="5" t="n">
+        <v>0.00725</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t># of shares*</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Note 12) - - 125,004</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" s="5" t="n">
+        <v>0.125004</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t># of shares*</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>-2.449707</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>-2.449707</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t># of shares*</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Balance, September 30, 2023 8,923,491 $ 18,074,487 $ 3,431,300 $</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" s="5" t="n">
+        <v>10.288977</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>-11.21681</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t># of shares*</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Shares issued for mineral properties (Note 9) 567,537 500,000 -</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t># of shares*</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Shares issued on issuance of debt (Note 11) 290,000 46,879 -</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="5" t="n">
+        <v>0.046879</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t># of shares*</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Balance, September 30, 2024 9,781,028 $ 18,621,366 $ 3,431,300 $</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" s="5" t="n">
         <v>5.39759</v>
       </c>
-      <c r="F109" s="5" t="n">
+      <c r="F120" s="5" t="n">
         <v>-16.655076</v>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>-</t>
         </is>
